--- a/downloads/invoice-template.xlsx
+++ b/downloads/invoice-template.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="חשבונית" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'חשבונית'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'חשבונית'!$A$1:$D$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,11 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00&quot; ₪&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ₪&quot;;(#,##0.00&quot; ₪&quot;)"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00 &quot;₪&quot;;[Red]-#,##0.00 &quot;₪&quot;"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,11 +36,10 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="20"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
       <color rgb="00666666"/>
       <sz val="10"/>
     </font>
@@ -46,22 +47,17 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00222222"/>
-      <sz val="10"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <color rgb="000000FF"/>
-      <sz val="10"/>
+      <color rgb="000000CC"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="000000FF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -72,19 +68,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00222222"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="001F5C4E"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00999999"/>
+      <color rgb="00666666"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -107,11 +97,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C99A3B"/>
+        <fgColor rgb="00E8F1EE"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,61 +111,17 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D9DED9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D9DED9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D9DED9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="00D9DED9"/>
       </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -184,48 +130,54 @@
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -591,241 +543,427 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>חשבונית עסקית</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" hidden="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>התאים הצהובים הם שדות למילוי — שאר התאים מתעדכנים אוטומטית</t>
+          <t>חשבונית / חשבון עסקה</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>ממלאים את התאים הצהובים — הסכומים, ההנחה, המע״מ והסה״כ מחושבים לבד. עוסק פטור: שיעור מע״מ 0%.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>סוג המסמך:</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>חשבונית מס</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>שם העסק:</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>שם העסק שלכם</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ח.פ / עוסק מורשה:</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>ח.פ / עוסק מורשה / פטור:</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>000000000</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>כתובת:</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>כתובת העסק, עיר</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>טלפון / מייל:</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>רחוב, עיר</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>טלפון / אימייל:</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>050-0000000 | info@business.co.il</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>לכבוד (לקוח):</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>שם הלקוח</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>מספר חשבונית:</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>2026-001</t>
-        </is>
-      </c>
-    </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>ח.פ / ת.ז של הלקוח:</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>מספר מסמך:</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2027-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>תאריך:</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="B13" s="6" t="n">
+        <v>46388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>לתשלום עד:</t>
+        </is>
+      </c>
+      <c r="B14" s="7">
+        <f>B13+30</f>
+        <v>46418.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>מספר הקצאה (אם נדרש):</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>תיאור</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>כמות</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>מחיר יחידה (₪)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>סה"כ (₪)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>שירות / מוצר לדוגמה 1</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>מחיר ליחידה (₪)</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>סה״כ (₪)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>שירות / מוצר לדוגמה</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C18" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="D15" s="9">
-        <f>IF(OR(B15="",C15=""),"",B15*C15)</f>
+      <c r="D18" s="11">
+        <f>IF(OR(B18="",C18=""),"",B18*C18)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>שורה נוספת לדוגמה</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>250</v>
+      </c>
+      <c r="D19" s="11">
+        <f>IF(OR(B19="",C19=""),"",B19*C19)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="11" t="str">
+        <f>IF(OR(B20="",C20=""),"",B20*C20)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>שירות / מוצר לדוגמה 2</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>250</v>
-      </c>
-      <c r="D16" s="9">
-        <f>IF(OR(B16="",C16=""),"",B16*C16)</f>
+    <row r="21">
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="11" t="str">
+        <f>IF(OR(B21="",C21=""),"",B21*C21)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="7" t="inlineStr"/>
-      <c r="C17" s="8" t="inlineStr"/>
-      <c r="D17" s="9">
-        <f>IF(OR(B17="",C17=""),"",B17*C17)</f>
+    <row r="22">
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="11" t="str">
+        <f>IF(OR(B22="",C22=""),"",B22*C22)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>סכום ביניים:</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="12">
-        <f>SUM(D15:D17)</f>
+    <row r="23">
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="11" t="str">
+        <f>IF(OR(B23="",C23=""),"",B23*C23)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>מע"מ (17%):</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="12">
-        <f>D19*0.17</f>
+    <row r="24">
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="11" t="str">
+        <f>IF(OR(B24="",C24=""),"",B24*C24)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>סה"כ לתשלום:</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="14">
-        <f>D19+D20</f>
+    <row r="25">
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="11" t="str">
+        <f>IF(OR(B25="",C25=""),"",B25*C25)</f>
         <v/>
       </c>
     </row>
-    <row r="23" hidden="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>שיעור מע"מ בישראל נכון למועד יצירת התבנית: 17%. יש לעדכן בהתאם לשיעור העדכני.</t>
+    <row r="26">
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="11" t="str">
+        <f>IF(OR(B26="",C26=""),"",B26*C26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="11" t="str">
+        <f>IF(OR(B27="",C27=""),"",B27*C27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="11" t="str">
+        <f>IF(OR(B28="",C28=""),"",B28*C28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="11" t="str">
+        <f>IF(OR(B29="",C29=""),"",B29*C29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>סכום ביניים</t>
+        </is>
+      </c>
+      <c r="D31" s="11">
+        <f>SUM(D18:D29)</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>הנחה (%)</t>
+        </is>
+      </c>
+      <c r="D32" s="11">
+        <f>-ROUND(D31*B32,2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>אחרי הנחה</t>
+        </is>
+      </c>
+      <c r="D33" s="11">
+        <f>D31+D32</f>
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>מע״מ</t>
+        </is>
+      </c>
+      <c r="D34" s="11">
+        <f>ROUND(D33*B34,2)</f>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="14" t="inlineStr">
+        <is>
+          <t>סה״כ לתשלום</t>
+        </is>
+      </c>
+      <c r="D35" s="15">
+        <f>D33+D34</f>
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>פרטי תשלום</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>בנק / סניף / חשבון:</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>בנק ___  סניף ___  חשבון ______</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>ביט / פייבוקס:</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>050-0000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>שיעור המע״מ בישראל מינואר 2025: 18% (התא הצהוב ליד המע״מ). חשבונית מס מעל הסכום שקבעה רשות המסים צריכה מספר הקצאה. התבנית אינה תחליף לתוכנה מאושרת להפקת חשבוניות.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A23:D23"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B8:D8"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B39:D39"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="B12:D12"/>
     <mergeCell ref="B7:D7"/>
     <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B38:D38"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup fitToHeight="1" fitToWidth="1"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="ערך לא ברשימה" error="יש לבחור מהרשימה (אפשר לערוך אותה בגיליון הרשימות)" type="list" errorStyle="warning">
+      <formula1>"חשבונית מס,חשבון עסקה,חשבונית מס / קבלה,קבלה,הצעת מחיר"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B18:C29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="יש להזין מספר" type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>